--- a/artfynd/A 55233-2021 artfynd.xlsx
+++ b/artfynd/A 55233-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55233-2021 artfynd.xlsx
+++ b/artfynd/A 55233-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99114477</v>
+        <v>99114468</v>
       </c>
       <c r="B2" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>373253.9153637183</v>
+        <v>373254</v>
       </c>
       <c r="R2" t="n">
-        <v>6919921.19026958</v>
+        <v>6919922</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>99114494</v>
       </c>
       <c r="B3" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373591.407625846</v>
+        <v>373592</v>
       </c>
       <c r="R3" t="n">
-        <v>6920104.312924018</v>
+        <v>6920104</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99114468</v>
+        <v>99114476</v>
       </c>
       <c r="B4" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>967</v>
+        <v>101410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>373253.9505397229</v>
+        <v>373457</v>
       </c>
       <c r="R4" t="n">
-        <v>6919922.1174481</v>
+        <v>6920067</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99114476</v>
+        <v>99114477</v>
       </c>
       <c r="B5" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373457.0562359926</v>
+        <v>373254</v>
       </c>
       <c r="R5" t="n">
-        <v>6920067.618745563</v>
+        <v>6919921</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55233-2021 artfynd.xlsx
+++ b/artfynd/A 55233-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114468</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114494</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114477</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>